--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/99.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/99.xlsx
@@ -426,13 +426,13 @@
         <v>-11.28880927821193</v>
       </c>
       <c r="E2">
-        <v>-7.560932475822353</v>
+        <v>-10.67316699385987</v>
       </c>
       <c r="F2">
-        <v>-5.032933513988937</v>
+        <v>-5.025161771015872</v>
       </c>
       <c r="G2">
-        <v>-6.283426515841665</v>
+        <v>-7.480218523198053</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-10.89382011805385</v>
       </c>
       <c r="E3">
-        <v>-7.947632456759348</v>
+        <v>-11.20968700886664</v>
       </c>
       <c r="F3">
-        <v>-5.026607272133757</v>
+        <v>-5.429262584388749</v>
       </c>
       <c r="G3">
-        <v>-6.014894924969222</v>
+        <v>-7.272511585518639</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-10.44521964215143</v>
       </c>
       <c r="E4">
-        <v>-8.974998297931506</v>
+        <v>-11.30395625228431</v>
       </c>
       <c r="F4">
-        <v>-4.725672163472933</v>
+        <v>-5.003639957523738</v>
       </c>
       <c r="G4">
-        <v>-5.490521064276362</v>
+        <v>-7.583103657467523</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.969533251166308</v>
       </c>
       <c r="E5">
-        <v>-9.286521081867166</v>
+        <v>-11.80425300370372</v>
       </c>
       <c r="F5">
-        <v>-5.094934328986271</v>
+        <v>-5.322712170468857</v>
       </c>
       <c r="G5">
-        <v>-5.550481665083642</v>
+        <v>-7.023320201686618</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.445575220697538</v>
       </c>
       <c r="E6">
-        <v>-10.37952715378051</v>
+        <v>-12.82655148246129</v>
       </c>
       <c r="F6">
-        <v>-5.273445847554759</v>
+        <v>-5.394998823506753</v>
       </c>
       <c r="G6">
-        <v>-4.931995615800381</v>
+        <v>-6.649327872115152</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.874460434597916</v>
       </c>
       <c r="E7">
-        <v>-10.74625656434367</v>
+        <v>-13.60813439686714</v>
       </c>
       <c r="F7">
-        <v>-5.633543784490927</v>
+        <v>-5.517887956079463</v>
       </c>
       <c r="G7">
-        <v>-5.136385386849445</v>
+        <v>-6.451396975413206</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.23429728466737</v>
       </c>
       <c r="E8">
-        <v>-11.25980815918353</v>
+        <v>-14.94654300373015</v>
       </c>
       <c r="F8">
-        <v>-5.115547423437534</v>
+        <v>-5.555344244931848</v>
       </c>
       <c r="G8">
-        <v>-4.415560443310693</v>
+        <v>-6.042739923500031</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.529248384871874</v>
       </c>
       <c r="E9">
-        <v>-12.67003836380819</v>
+        <v>-15.08068093231135</v>
       </c>
       <c r="F9">
-        <v>-5.524669800006182</v>
+        <v>-5.437926479054629</v>
       </c>
       <c r="G9">
-        <v>-4.015275761066335</v>
+        <v>-6.225180777623727</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.750896378100188</v>
       </c>
       <c r="E10">
-        <v>-13.76298103708542</v>
+        <v>-15.52943912104946</v>
       </c>
       <c r="F10">
-        <v>-5.518051144457814</v>
+        <v>-5.86174989192076</v>
       </c>
       <c r="G10">
-        <v>-3.505256425831756</v>
+        <v>-5.588622460241585</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.90868040788053</v>
       </c>
       <c r="E11">
-        <v>-14.19308644138594</v>
+        <v>-16.79378453551702</v>
       </c>
       <c r="F11">
-        <v>-5.564505160039408</v>
+        <v>-5.592760772148899</v>
       </c>
       <c r="G11">
-        <v>-3.149564792001381</v>
+        <v>-5.032334940550151</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.022301726006085</v>
       </c>
       <c r="E12">
-        <v>-14.72542214640961</v>
+        <v>-17.5696615726732</v>
       </c>
       <c r="F12">
-        <v>-5.661550886379578</v>
+        <v>-5.984778190217139</v>
       </c>
       <c r="G12">
-        <v>-2.733462323170385</v>
+        <v>-3.725262040189562</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.112725329509236</v>
       </c>
       <c r="E13">
-        <v>-16.44620604153229</v>
+        <v>-18.55238571707774</v>
       </c>
       <c r="F13">
-        <v>-5.15870288002118</v>
+        <v>-5.719487730898778</v>
       </c>
       <c r="G13">
-        <v>-2.0992776669399</v>
+        <v>-3.577356797131543</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.229947575764642</v>
       </c>
       <c r="E14">
-        <v>-16.37375498588356</v>
+        <v>-17.8513915261124</v>
       </c>
       <c r="F14">
-        <v>-5.520870078729541</v>
+        <v>-5.500655428999025</v>
       </c>
       <c r="G14">
-        <v>-1.760552578998291</v>
+        <v>-2.823254249832038</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.412788437100676</v>
       </c>
       <c r="E15">
-        <v>-17.67574107630288</v>
+        <v>-19.51335960082345</v>
       </c>
       <c r="F15">
-        <v>-5.445829104077337</v>
+        <v>-5.543074466961581</v>
       </c>
       <c r="G15">
-        <v>-1.011985263840447</v>
+        <v>-2.975201668993507</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.717161332591981</v>
       </c>
       <c r="E16">
-        <v>-18.99704563683891</v>
+        <v>-20.40705394623719</v>
       </c>
       <c r="F16">
-        <v>-4.913241879591033</v>
+        <v>-5.418997455533257</v>
       </c>
       <c r="G16">
-        <v>-0.1113248655174061</v>
+        <v>-2.555447668432695</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.183232514316859</v>
       </c>
       <c r="E17">
-        <v>-20.24722598461048</v>
+        <v>-21.35315632134171</v>
       </c>
       <c r="F17">
-        <v>-4.990878129316209</v>
+        <v>-5.153401328643263</v>
       </c>
       <c r="G17">
-        <v>-0.05146689162184379</v>
+        <v>-1.837284403507518</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.8442055482096968</v>
       </c>
       <c r="E18">
-        <v>-19.99167966788363</v>
+        <v>-22.16951338765246</v>
       </c>
       <c r="F18">
-        <v>-4.440307048515129</v>
+        <v>-4.340763794455517</v>
       </c>
       <c r="G18">
-        <v>-0.01893416060742583</v>
+        <v>-2.370798680434306</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.7224733186080675</v>
       </c>
       <c r="E19">
-        <v>-21.50608741705474</v>
+        <v>-23.14334813757995</v>
       </c>
       <c r="F19">
-        <v>-4.343325106464974</v>
+        <v>-4.30881366372954</v>
       </c>
       <c r="G19">
-        <v>-0.1084115854428475</v>
+        <v>-1.628153931246218</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.8131255137534718</v>
       </c>
       <c r="E20">
-        <v>-23.32815063335897</v>
+        <v>-23.60330524253902</v>
       </c>
       <c r="F20">
-        <v>-3.77812091549344</v>
+        <v>-4.140943352817415</v>
       </c>
       <c r="G20">
-        <v>0.1510226262876784</v>
+        <v>-1.792247741991273</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.111199035718615</v>
       </c>
       <c r="E21">
-        <v>-23.0285513214855</v>
+        <v>-24.17020678966324</v>
       </c>
       <c r="F21">
-        <v>-3.773742993769645</v>
+        <v>-3.526218530139124</v>
       </c>
       <c r="G21">
-        <v>-0.2243005425905746</v>
+        <v>-2.093633186795443</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.583186522909841</v>
       </c>
       <c r="E22">
-        <v>-23.77039234800004</v>
+        <v>-24.5356274712382</v>
       </c>
       <c r="F22">
-        <v>-2.955698705543826</v>
+        <v>-3.224994321254723</v>
       </c>
       <c r="G22">
-        <v>-0.9877752443117566</v>
+        <v>-2.106309265665312</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.199312702139399</v>
       </c>
       <c r="E23">
-        <v>-23.89070031696182</v>
+        <v>-26.53706354298624</v>
       </c>
       <c r="F23">
-        <v>-3.086645367843567</v>
+        <v>-3.249619199037744</v>
       </c>
       <c r="G23">
-        <v>-0.2088734003775709</v>
+        <v>-2.353901656001865</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.915457169285414</v>
       </c>
       <c r="E24">
-        <v>-24.9290024228625</v>
+        <v>-26.79230645195457</v>
       </c>
       <c r="F24">
-        <v>-2.522482434697352</v>
+        <v>-2.600419381789744</v>
       </c>
       <c r="G24">
-        <v>-1.388927289487403</v>
+        <v>-3.375668431242524</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-3.683674343415071</v>
       </c>
       <c r="E25">
-        <v>-25.0660929164967</v>
+        <v>-26.62199054452609</v>
       </c>
       <c r="F25">
-        <v>-2.309561362583976</v>
+        <v>-2.556467035764605</v>
       </c>
       <c r="G25">
-        <v>-1.343145755224822</v>
+        <v>-3.274749761023382</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.459386715695065</v>
       </c>
       <c r="E26">
-        <v>-25.5224000714056</v>
+        <v>-27.27001517502372</v>
       </c>
       <c r="F26">
-        <v>-2.414490661496589</v>
+        <v>-2.655567113263718</v>
       </c>
       <c r="G26">
-        <v>-1.937772702806556</v>
+        <v>-3.678050350254015</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.190663902267167</v>
       </c>
       <c r="E27">
-        <v>-25.21673713283586</v>
+        <v>-27.45088695536408</v>
       </c>
       <c r="F27">
-        <v>-1.939298529248056</v>
+        <v>-2.216052765053759</v>
       </c>
       <c r="G27">
-        <v>-2.858005046357767</v>
+        <v>-4.528036228007432</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.838880806624859</v>
       </c>
       <c r="E28">
-        <v>-25.44886671046905</v>
+        <v>-26.47238787720869</v>
       </c>
       <c r="F28">
-        <v>-2.078943877644593</v>
+        <v>-2.11513110763589</v>
       </c>
       <c r="G28">
-        <v>-2.909129801120732</v>
+        <v>-4.342387455256183</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-6.364611515642948</v>
       </c>
       <c r="E29">
-        <v>-25.17291056138963</v>
+        <v>-26.9794139410035</v>
       </c>
       <c r="F29">
-        <v>-2.203239578067256</v>
+        <v>-2.049575768113142</v>
       </c>
       <c r="G29">
-        <v>-3.095586346983564</v>
+        <v>-4.807413166066527</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.743683025906173</v>
       </c>
       <c r="E30">
-        <v>-25.01027947435217</v>
+        <v>-26.98094003674408</v>
       </c>
       <c r="F30">
-        <v>-1.915138365578005</v>
+        <v>-2.270889858751683</v>
       </c>
       <c r="G30">
-        <v>-3.505094209100331</v>
+        <v>-4.572374364414891</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.958933552213957</v>
       </c>
       <c r="E31">
-        <v>-24.91742311482489</v>
+        <v>-26.06639659699902</v>
       </c>
       <c r="F31">
-        <v>-1.997738192780755</v>
+        <v>-2.391494354027472</v>
       </c>
       <c r="G31">
-        <v>-2.910377876789038</v>
+        <v>-4.901813372118846</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.000798625341204</v>
       </c>
       <c r="E32">
-        <v>-24.60551088212457</v>
+        <v>-25.8367803224401</v>
       </c>
       <c r="F32">
-        <v>-2.036797372557557</v>
+        <v>-2.616146765299295</v>
       </c>
       <c r="G32">
-        <v>-3.817483907277039</v>
+        <v>-4.832040314333166</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.872817768983304</v>
       </c>
       <c r="E33">
-        <v>-24.28819165145909</v>
+        <v>-25.85954043280265</v>
       </c>
       <c r="F33">
-        <v>-2.28710100882447</v>
+        <v>-2.578556280927657</v>
       </c>
       <c r="G33">
-        <v>-3.390784382174837</v>
+        <v>-5.014312330634358</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.585062208829558</v>
       </c>
       <c r="E34">
-        <v>-23.80655221295128</v>
+        <v>-25.51006903668271</v>
       </c>
       <c r="F34">
-        <v>-2.206246551739419</v>
+        <v>-2.528966066359064</v>
       </c>
       <c r="G34">
-        <v>-3.610660885256611</v>
+        <v>-5.273094364893648</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.160383054884335</v>
       </c>
       <c r="E35">
-        <v>-24.06587527700053</v>
+        <v>-25.91661279072132</v>
       </c>
       <c r="F35">
-        <v>-2.050894529018399</v>
+        <v>-2.549892283688585</v>
       </c>
       <c r="G35">
-        <v>-4.263970563067466</v>
+        <v>-4.77460565977235</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.628721828038076</v>
       </c>
       <c r="E36">
-        <v>-23.01840301123431</v>
+        <v>-25.35044032791233</v>
       </c>
       <c r="F36">
-        <v>-2.386585448798482</v>
+        <v>-2.635146200049905</v>
       </c>
       <c r="G36">
-        <v>-3.321981314232163</v>
+        <v>-4.406449821986619</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.020619500062383</v>
       </c>
       <c r="E37">
-        <v>-23.00810526134087</v>
+        <v>-24.04492655624104</v>
       </c>
       <c r="F37">
-        <v>-2.706645075687738</v>
+        <v>-2.826140387011178</v>
       </c>
       <c r="G37">
-        <v>-2.88256598371362</v>
+        <v>-4.333117927746223</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.375446210725894</v>
       </c>
       <c r="E38">
-        <v>-22.79973658682593</v>
+        <v>-24.1799837650458</v>
       </c>
       <c r="F38">
-        <v>-2.629800745199639</v>
+        <v>-2.933819865701086</v>
       </c>
       <c r="G38">
-        <v>-2.389049717992307</v>
+        <v>-3.893070283029679</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.723099882775499</v>
       </c>
       <c r="E39">
-        <v>-21.71593237409618</v>
+        <v>-23.42828425061657</v>
       </c>
       <c r="F39">
-        <v>-2.72413025482603</v>
+        <v>-3.181821468955619</v>
       </c>
       <c r="G39">
-        <v>-1.898483148346485</v>
+        <v>-3.407224551322857</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.096032738814689</v>
       </c>
       <c r="E40">
-        <v>-21.32870256170029</v>
+        <v>-22.65883311807727</v>
       </c>
       <c r="F40">
-        <v>-2.873140296711217</v>
+        <v>-2.909074874644659</v>
       </c>
       <c r="G40">
-        <v>-1.762456142683371</v>
+        <v>-3.476944640379909</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.518446398168524</v>
       </c>
       <c r="E41">
-        <v>-21.44001245280883</v>
+        <v>-22.77200421200296</v>
       </c>
       <c r="F41">
-        <v>-3.016737785986511</v>
+        <v>-3.386839087678885</v>
       </c>
       <c r="G41">
-        <v>-1.440022249340515</v>
+        <v>-2.923884902589264</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.006703094398644</v>
       </c>
       <c r="E42">
-        <v>-19.85755532472445</v>
+        <v>-21.65968419844691</v>
       </c>
       <c r="F42">
-        <v>-2.950581051729331</v>
+        <v>-3.646089920263435</v>
       </c>
       <c r="G42">
-        <v>-1.081920538357551</v>
+        <v>-3.788655676721066</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.578898673567267</v>
       </c>
       <c r="E43">
-        <v>-19.38759029220842</v>
+        <v>-21.75311567417316</v>
       </c>
       <c r="F43">
-        <v>-3.508713470183165</v>
+        <v>-3.355598039449704</v>
       </c>
       <c r="G43">
-        <v>-1.35996332656432</v>
+        <v>-2.824783721871181</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.237614499097472</v>
       </c>
       <c r="E44">
-        <v>-19.55307431787072</v>
+        <v>-21.69904116604757</v>
       </c>
       <c r="F44">
-        <v>-3.361277326363298</v>
+        <v>-3.517853676105655</v>
       </c>
       <c r="G44">
-        <v>-1.352613915467138</v>
+        <v>-2.010442487939097</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.9897220130186752</v>
       </c>
       <c r="E45">
-        <v>-18.94015894635456</v>
+        <v>-20.49270550361827</v>
       </c>
       <c r="F45">
-        <v>-3.554663838383857</v>
+        <v>-3.675513530410874</v>
       </c>
       <c r="G45">
-        <v>-0.785196341672674</v>
+        <v>-2.100545605881441</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.8281396078447025</v>
       </c>
       <c r="E46">
-        <v>-18.5920325070149</v>
+        <v>-19.87180643242659</v>
       </c>
       <c r="F46">
-        <v>-3.192075000667471</v>
+        <v>-3.684150088952461</v>
       </c>
       <c r="G46">
-        <v>-0.9476348796480933</v>
+        <v>-3.067552647357016</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.7445136884183652</v>
       </c>
       <c r="E47">
-        <v>-17.61687544267717</v>
+        <v>-19.99427448349002</v>
       </c>
       <c r="F47">
-        <v>-3.486581149915168</v>
+        <v>-4.076299217437747</v>
       </c>
       <c r="G47">
-        <v>-1.34710516768979</v>
+        <v>-2.860938189705562</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.7278169253895582</v>
       </c>
       <c r="E48">
-        <v>-16.42744457371851</v>
+        <v>-18.97766829656009</v>
       </c>
       <c r="F48">
-        <v>-3.778974962285726</v>
+        <v>-3.683434379516443</v>
       </c>
       <c r="G48">
-        <v>-1.034007012767679</v>
+        <v>-2.462100215861866</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.7603000698215197</v>
       </c>
       <c r="E49">
-        <v>-17.0514230072354</v>
+        <v>-19.00008877137207</v>
       </c>
       <c r="F49">
-        <v>-3.833604135765548</v>
+        <v>-4.101165150134983</v>
       </c>
       <c r="G49">
-        <v>-1.368358870051911</v>
+        <v>-1.785970947648815</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.8305036427066609</v>
       </c>
       <c r="E50">
-        <v>-15.70472276446436</v>
+        <v>-18.02100099159568</v>
       </c>
       <c r="F50">
-        <v>-3.800679016606476</v>
+        <v>-4.15120931004031</v>
       </c>
       <c r="G50">
-        <v>-0.8663080179303574</v>
+        <v>-2.336408733372356</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.9203737864596133</v>
       </c>
       <c r="E51">
-        <v>-15.69969615831584</v>
+        <v>-17.29793954679096</v>
       </c>
       <c r="F51">
-        <v>-3.647502286685208</v>
+        <v>-3.787329875910362</v>
       </c>
       <c r="G51">
-        <v>-0.4057614752346462</v>
+        <v>-2.935686997436766</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.017804045199477</v>
       </c>
       <c r="E52">
-        <v>-14.81073406824011</v>
+        <v>-17.34486359445843</v>
       </c>
       <c r="F52">
-        <v>-3.87760452710005</v>
+        <v>-3.915738420487925</v>
       </c>
       <c r="G52">
-        <v>-1.36936527589585</v>
+        <v>-2.738722780032287</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.110125611748944</v>
       </c>
       <c r="E53">
-        <v>-14.28459331565893</v>
+        <v>-17.29604211618174</v>
       </c>
       <c r="F53">
-        <v>-3.685819249269102</v>
+        <v>-3.903650883346274</v>
       </c>
       <c r="G53">
-        <v>-1.025104955812578</v>
+        <v>-2.747684426807095</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.188346579836397</v>
       </c>
       <c r="E54">
-        <v>-13.11918600131096</v>
+        <v>-15.81455637304639</v>
       </c>
       <c r="F54">
-        <v>-3.923172189560648</v>
+        <v>-3.879552847231434</v>
       </c>
       <c r="G54">
-        <v>-1.164545133926681</v>
+        <v>-2.4095254421527</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.247843623372074</v>
       </c>
       <c r="E55">
-        <v>-13.24101100906531</v>
+        <v>-15.5962341126626</v>
       </c>
       <c r="F55">
-        <v>-3.857664895347263</v>
+        <v>-3.991730360918543</v>
       </c>
       <c r="G55">
-        <v>-0.9334061549203059</v>
+        <v>-2.753113721491499</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.285185461824758</v>
       </c>
       <c r="E56">
-        <v>-13.14297860374726</v>
+        <v>-15.54220488927708</v>
       </c>
       <c r="F56">
-        <v>-4.031612937893728</v>
+        <v>-4.135480269795952</v>
       </c>
       <c r="G56">
-        <v>-1.476044295353325</v>
+        <v>-2.69047157879741</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-1.302895899872398</v>
       </c>
       <c r="E57">
-        <v>-12.15338023579907</v>
+        <v>-14.27231662262414</v>
       </c>
       <c r="F57">
-        <v>-3.893929163507019</v>
+        <v>-3.899472598166553</v>
       </c>
       <c r="G57">
-        <v>-1.12598389948525</v>
+        <v>-3.422214701524677</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-1.303590884766582</v>
       </c>
       <c r="E58">
-        <v>-11.83784522389261</v>
+        <v>-14.78066952930319</v>
       </c>
       <c r="F58">
-        <v>-3.778471314904824</v>
+        <v>-3.701178837651811</v>
       </c>
       <c r="G58">
-        <v>-1.179608116130365</v>
+        <v>-3.35179608735884</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.295299714558521</v>
       </c>
       <c r="E59">
-        <v>-11.62070489522482</v>
+        <v>-13.99033307464051</v>
       </c>
       <c r="F59">
-        <v>-4.203919984615248</v>
+        <v>-3.922429972367739</v>
       </c>
       <c r="G59">
-        <v>-1.763485722346085</v>
+        <v>-3.524752228512524</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.285635621794495</v>
       </c>
       <c r="E60">
-        <v>-11.05239499268421</v>
+        <v>-13.93488191041659</v>
       </c>
       <c r="F60">
-        <v>-3.720034964841736</v>
+        <v>-4.182224213968525</v>
       </c>
       <c r="G60">
-        <v>-1.974470100109377</v>
+        <v>-3.536531149541251</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.28216207862105</v>
       </c>
       <c r="E61">
-        <v>-10.18720739114875</v>
+        <v>-13.03808103183358</v>
       </c>
       <c r="F61">
-        <v>-3.958402655201711</v>
+        <v>-4.135159691611069</v>
       </c>
       <c r="G61">
-        <v>-2.032983992515995</v>
+        <v>-3.97873395940386</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.293270155519674</v>
       </c>
       <c r="E62">
-        <v>-9.856026501545797</v>
+        <v>-12.77174789002046</v>
       </c>
       <c r="F62">
-        <v>-3.989711629557921</v>
+        <v>-3.908357666928981</v>
       </c>
       <c r="G62">
-        <v>-2.699489504846385</v>
+        <v>-4.07317058145711</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.322248586638072</v>
       </c>
       <c r="E63">
-        <v>-9.70609325562584</v>
+        <v>-12.6290692594608</v>
       </c>
       <c r="F63">
-        <v>-4.107574228730443</v>
+        <v>-4.23463501954365</v>
       </c>
       <c r="G63">
-        <v>-2.876285878825623</v>
+        <v>-3.639300414716846</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.37490145841054</v>
       </c>
       <c r="E64">
-        <v>-8.778906316451364</v>
+        <v>-12.8037098595666</v>
       </c>
       <c r="F64">
-        <v>-4.193502436157641</v>
+        <v>-4.14601047622034</v>
       </c>
       <c r="G64">
-        <v>-3.243514763860358</v>
+        <v>-4.369136663213493</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-1.451370043467778</v>
       </c>
       <c r="E65">
-        <v>-8.298403524919486</v>
+        <v>-12.53054777894992</v>
       </c>
       <c r="F65">
-        <v>-4.182853773194653</v>
+        <v>-4.22344377593183</v>
       </c>
       <c r="G65">
-        <v>-3.229729652234833</v>
+        <v>-3.915532334513634</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-1.552223257264363</v>
       </c>
       <c r="E66">
-        <v>-9.814183401714923</v>
+        <v>-11.67218458774402</v>
       </c>
       <c r="F66">
-        <v>-4.431761610387849</v>
+        <v>-4.098999797744065</v>
       </c>
       <c r="G66">
-        <v>-3.037439925131805</v>
+        <v>-4.567176807918235</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.676292229719713</v>
       </c>
       <c r="E67">
-        <v>-8.342402178378011</v>
+        <v>-11.66442278329487</v>
       </c>
       <c r="F67">
-        <v>-4.619471320597023</v>
+        <v>-4.436175151909964</v>
       </c>
       <c r="G67">
-        <v>-3.44059816090425</v>
+        <v>-4.497373955222702</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.818100803538766</v>
       </c>
       <c r="E68">
-        <v>-8.912912919286345</v>
+        <v>-12.16912121144973</v>
       </c>
       <c r="F68">
-        <v>-4.540405308734615</v>
+        <v>-4.363585316402644</v>
       </c>
       <c r="G68">
-        <v>-3.341059988174984</v>
+        <v>-5.140970492421335</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.975565491169161</v>
       </c>
       <c r="E69">
-        <v>-9.000412094062552</v>
+        <v>-11.85457793535096</v>
       </c>
       <c r="F69">
-        <v>-4.551628858675145</v>
+        <v>-4.302571086982043</v>
       </c>
       <c r="G69">
-        <v>-3.913502970098061</v>
+        <v>-4.182405342070902</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.139822043897727</v>
       </c>
       <c r="E70">
-        <v>-9.313257192408452</v>
+        <v>-11.8677693801353</v>
       </c>
       <c r="F70">
-        <v>-4.505027393695854</v>
+        <v>-4.715901569956912</v>
       </c>
       <c r="G70">
-        <v>-2.948108164300111</v>
+        <v>-4.567031143914507</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.307259810697388</v>
       </c>
       <c r="E71">
-        <v>-8.847961016594329</v>
+        <v>-11.6917747663012</v>
       </c>
       <c r="F71">
-        <v>-4.836646059323774</v>
+        <v>-4.874393933501945</v>
       </c>
       <c r="G71">
-        <v>-3.167253036817707</v>
+        <v>-4.390029516111834</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.4717442449408</v>
       </c>
       <c r="E72">
-        <v>-9.210768768666856</v>
+        <v>-11.24884925208497</v>
       </c>
       <c r="F72">
-        <v>-4.796848804191078</v>
+        <v>-4.722696667762077</v>
       </c>
       <c r="G72">
-        <v>-3.172155954761367</v>
+        <v>-3.96846795768658</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.627942437333227</v>
       </c>
       <c r="E73">
-        <v>-8.725778259393376</v>
+        <v>-11.35036405391492</v>
       </c>
       <c r="F73">
-        <v>-4.814811951320785</v>
+        <v>-4.718037929488733</v>
       </c>
       <c r="G73">
-        <v>-3.577926210964298</v>
+        <v>-4.029438274883338</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.775058778960446</v>
       </c>
       <c r="E74">
-        <v>-9.374989350081014</v>
+        <v>-12.05602710158217</v>
       </c>
       <c r="F74">
-        <v>-5.028881140654442</v>
+        <v>-4.857660911965395</v>
       </c>
       <c r="G74">
-        <v>-2.974195263149568</v>
+        <v>-4.193830034726927</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.908264535999196</v>
       </c>
       <c r="E75">
-        <v>-9.3762210950111</v>
+        <v>-11.67386465160086</v>
       </c>
       <c r="F75">
-        <v>-4.582420103404606</v>
+        <v>-4.982560492224699</v>
       </c>
       <c r="G75">
-        <v>-2.189132493966799</v>
+        <v>-4.16329025212715</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.030213908056127</v>
       </c>
       <c r="E76">
-        <v>-10.02937195808541</v>
+        <v>-11.55561713831258</v>
       </c>
       <c r="F76">
-        <v>-4.965356958003358</v>
+        <v>-5.030924723037148</v>
       </c>
       <c r="G76">
-        <v>-2.665649108343954</v>
+        <v>-3.838075500531306</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.139736715289098</v>
       </c>
       <c r="E77">
-        <v>-9.622221388529777</v>
+        <v>-12.49762577291416</v>
       </c>
       <c r="F77">
-        <v>-5.132890123382545</v>
+        <v>-5.142464393824102</v>
       </c>
       <c r="G77">
-        <v>-2.243855811730952</v>
+        <v>-3.887998527263516</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.239123769331716</v>
       </c>
       <c r="E78">
-        <v>-11.73205101412542</v>
+        <v>-12.78403364000327</v>
       </c>
       <c r="F78">
-        <v>-4.99955113602352</v>
+        <v>-5.301158879015417</v>
       </c>
       <c r="G78">
-        <v>-1.570765624322952</v>
+        <v>-2.973692060227599</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.331978037273165</v>
       </c>
       <c r="E79">
-        <v>-11.20438869427766</v>
+        <v>-13.24575232135134</v>
       </c>
       <c r="F79">
-        <v>-5.144941212358472</v>
+        <v>-5.344523084184568</v>
       </c>
       <c r="G79">
-        <v>-1.910434217743254</v>
+        <v>-3.61638812903955</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.41746437118515</v>
       </c>
       <c r="E80">
-        <v>-11.68166721231608</v>
+        <v>-14.11316793209857</v>
       </c>
       <c r="F80">
-        <v>-5.381202364413127</v>
+        <v>-5.362287423137603</v>
       </c>
       <c r="G80">
-        <v>-1.907371963119428</v>
+        <v>-3.145175008616307</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.500567226042195</v>
       </c>
       <c r="E81">
-        <v>-13.17617231822348</v>
+        <v>-14.77457420328886</v>
       </c>
       <c r="F81">
-        <v>-5.586149571907156</v>
+        <v>-5.220238152538141</v>
       </c>
       <c r="G81">
-        <v>-1.865970280605303</v>
+        <v>-2.943423742362043</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.577724039697645</v>
       </c>
       <c r="E82">
-        <v>-12.95890972075748</v>
+        <v>-16.20356134725329</v>
       </c>
       <c r="F82">
-        <v>-5.499670500157096</v>
+        <v>-5.529384867262917</v>
       </c>
       <c r="G82">
-        <v>-2.161469575440649</v>
+        <v>-3.060292620989394</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.651575808644322</v>
       </c>
       <c r="E83">
-        <v>-14.23484802868467</v>
+        <v>-16.69521324179205</v>
       </c>
       <c r="F83">
-        <v>-5.9857134170149</v>
+        <v>-5.484743319558649</v>
       </c>
       <c r="G83">
-        <v>-1.459448530564958</v>
+        <v>-2.585149883011036</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.721756143174707</v>
       </c>
       <c r="E84">
-        <v>-15.24081230169658</v>
+        <v>-17.94236404045249</v>
       </c>
       <c r="F84">
-        <v>-5.363070230333249</v>
+        <v>-5.908227101789632</v>
       </c>
       <c r="G84">
-        <v>-1.139196286732481</v>
+        <v>-2.353093882890283</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.786107144951226</v>
       </c>
       <c r="E85">
-        <v>-17.06547939055521</v>
+        <v>-18.94784829521958</v>
       </c>
       <c r="F85">
-        <v>-6.045591954726262</v>
+        <v>-5.510122011678217</v>
       </c>
       <c r="G85">
-        <v>-0.8855654613322979</v>
+        <v>-3.131509076630196</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.849226049743147</v>
       </c>
       <c r="E86">
-        <v>-17.38565155984552</v>
+        <v>-20.58321611360958</v>
       </c>
       <c r="F86">
-        <v>-5.817118284625325</v>
+        <v>-5.866838552876157</v>
       </c>
       <c r="G86">
-        <v>-0.6239661528190887</v>
+        <v>-2.530029299782171</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.907851362832523</v>
       </c>
       <c r="E87">
-        <v>-19.09793098078179</v>
+        <v>-21.80681431895612</v>
       </c>
       <c r="F87">
-        <v>-6.062931341201661</v>
+        <v>-6.063557586958178</v>
       </c>
       <c r="G87">
-        <v>-1.541682481760454</v>
+        <v>-2.524897954196301</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.968916084401915</v>
       </c>
       <c r="E88">
-        <v>-20.40083635142466</v>
+        <v>-22.32487627390761</v>
       </c>
       <c r="F88">
-        <v>-6.070412327216344</v>
+        <v>-6.086673179333299</v>
       </c>
       <c r="G88">
-        <v>-1.18644439266896</v>
+        <v>-2.506074192260005</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.033506180878494</v>
       </c>
       <c r="E89">
-        <v>-22.6478696825047</v>
+        <v>-23.50980583970265</v>
       </c>
       <c r="F89">
-        <v>-6.194823999075399</v>
+        <v>-6.0250973168136</v>
       </c>
       <c r="G89">
-        <v>-1.530449800745707</v>
+        <v>-2.512619140791144</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.106286885778315</v>
       </c>
       <c r="E90">
-        <v>-24.16619456169245</v>
+        <v>-25.58866070308583</v>
       </c>
       <c r="F90">
-        <v>-6.239915350279388</v>
+        <v>-6.169891796985939</v>
       </c>
       <c r="G90">
-        <v>-0.753150260852529</v>
+        <v>-1.97227520841684</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.196398389408042</v>
       </c>
       <c r="E91">
-        <v>-26.97263028694001</v>
+        <v>-27.71587966887093</v>
       </c>
       <c r="F91">
-        <v>-5.96247356952936</v>
+        <v>-6.549561570548051</v>
       </c>
       <c r="G91">
-        <v>-1.737504560953884</v>
+        <v>-2.900287333985339</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.305327833239915</v>
       </c>
       <c r="E92">
-        <v>-27.44264060419611</v>
+        <v>-29.5445272863823</v>
       </c>
       <c r="F92">
-        <v>-6.268332079848723</v>
+        <v>-6.610700883446474</v>
       </c>
       <c r="G92">
-        <v>-2.158423873544519</v>
+        <v>-3.026978601227708</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.447033477981773</v>
       </c>
       <c r="E93">
-        <v>-30.83052559931754</v>
+        <v>-32.13096748010023</v>
       </c>
       <c r="F93">
-        <v>-6.38604515870504</v>
+        <v>-6.373805201961274</v>
       </c>
       <c r="G93">
-        <v>-2.424075289797797</v>
+        <v>-3.5366701924539</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.621490926087852</v>
       </c>
       <c r="E94">
-        <v>-33.12346859988734</v>
+        <v>-33.6425154979355</v>
       </c>
       <c r="F94">
-        <v>-6.329159512419992</v>
+        <v>-6.409049749848185</v>
       </c>
       <c r="G94">
-        <v>-2.765207144346457</v>
+        <v>-3.144774432606055</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.837556119255733</v>
       </c>
       <c r="E95">
-        <v>-35.10554770948959</v>
+        <v>-35.69830910743462</v>
       </c>
       <c r="F95">
-        <v>-6.402864744635182</v>
+        <v>-6.555917633629732</v>
       </c>
       <c r="G95">
-        <v>-3.215451269323956</v>
+        <v>-4.494745382064521</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.103304553732866</v>
       </c>
       <c r="E96">
-        <v>-37.09035975315548</v>
+        <v>-37.8189074442205</v>
       </c>
       <c r="F96">
-        <v>-6.670924021997401</v>
+        <v>-6.653467421534505</v>
       </c>
       <c r="G96">
-        <v>-3.962171300070886</v>
+        <v>-4.947879613297804</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.410080699233078</v>
       </c>
       <c r="E97">
-        <v>-39.68758903619668</v>
+        <v>-40.53125732924769</v>
       </c>
       <c r="F97">
-        <v>-6.802058723697576</v>
+        <v>-7.044671796996899</v>
       </c>
       <c r="G97">
-        <v>-4.091454724470505</v>
+        <v>-4.770765426946795</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.77738636235749</v>
       </c>
       <c r="E98">
-        <v>-42.36318582617763</v>
+        <v>-43.79489005454666</v>
       </c>
       <c r="F98">
-        <v>-6.470491831032331</v>
+        <v>-6.754782553468704</v>
       </c>
       <c r="G98">
-        <v>-4.583034321051344</v>
+        <v>-5.460693048967529</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.176432860812628</v>
       </c>
       <c r="E99">
-        <v>-44.74669830690083</v>
+        <v>-46.05737227470386</v>
       </c>
       <c r="F99">
-        <v>-6.751425594568859</v>
+        <v>-6.85276474915774</v>
       </c>
       <c r="G99">
-        <v>-5.189539506027983</v>
+        <v>-6.220824099694046</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.642403646364502</v>
       </c>
       <c r="E100">
-        <v>-47.18856696792389</v>
+        <v>-47.81852751560492</v>
       </c>
       <c r="F100">
-        <v>-6.749301660548082</v>
+        <v>-6.879176415428599</v>
       </c>
       <c r="G100">
-        <v>-6.382044356911014</v>
+        <v>-6.560870095305826</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.116379246128259</v>
       </c>
       <c r="E101">
-        <v>-49.43673581386135</v>
+        <v>-49.72591850339867</v>
       </c>
       <c r="F101">
-        <v>-6.437309503794689</v>
+        <v>-6.995115131308119</v>
       </c>
       <c r="G101">
-        <v>-6.224134645233318</v>
+        <v>-7.295274896646667</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.678580675947889</v>
       </c>
       <c r="E102">
-        <v>-51.96973095734075</v>
+        <v>-52.96098448253874</v>
       </c>
       <c r="F102">
-        <v>-6.715027959257252</v>
+        <v>-7.215436423614405</v>
       </c>
       <c r="G102">
-        <v>-6.83162306223512</v>
+        <v>-7.512893607670659</v>
       </c>
     </row>
   </sheetData>
